--- a/resultados_estatisticos.xlsx
+++ b/resultados_estatisticos.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qui-quadrado e Cramer V" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chi2 e Cramer V" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mann-Whitney Salarial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tendência Temporal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +475,11 @@
           <t>% células (exp≥5)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Pressuposto OK</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -484,13 +488,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15557</v>
+        <v>12422</v>
       </c>
       <c r="C2" t="n">
-        <v>104.49</v>
+        <v>47.763</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -501,7 +505,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.082</v>
+        <v>0.0607</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,6 +515,11 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>100%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -538,7 +547,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.1092</v>
+        <v>0.1059</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -548,6 +557,11 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>100%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -575,7 +589,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0699</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -585,6 +599,11 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>100%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -612,7 +631,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.106</v>
+        <v>0.1037</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -622,6 +641,11 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -649,7 +673,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.0624</v>
+        <v>0.0608</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -659,6 +683,11 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -686,7 +715,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0794</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -696,6 +725,11 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -723,7 +757,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.1786</v>
+        <v>0.1773</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -733,6 +767,11 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -760,7 +799,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.0318</v>
+        <v>0.0278</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -770,6 +809,11 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -784,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,57 +839,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N Masculino</t>
+          <t>N Masc</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>N Feminino</t>
+          <t>N Fem</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Mediana Masc (rank)</t>
+          <t>Mediana Masc</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mediana Fem (rank)</t>
+          <t>Mediana Fem</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Faixa modal Masc</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Faixa modal Fem</t>
+          <t>p-valor</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Significativo</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>p-valor</t>
+          <t>r (rank-biserial)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Significativo</t>
+          <t>Direção</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>r (effect size)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Magnitude r</t>
+          <t>Magnitude</t>
         </is>
       </c>
     </row>
@@ -861,48 +900,45 @@
       <c r="C2" t="n">
         <v>3538</v>
       </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>23712840</v>
       </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.1264</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Masc &gt; Fem</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Grande</t>
+          <t>Pequeno</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Brasil — 2021</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -911,46 +947,45 @@
       <c r="C3" t="n">
         <v>430</v>
       </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>454266</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.000131</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>0.1167</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.0794</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Negligenciável</t>
+          <t>Masc &gt; Fem</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Brasil — 2022</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -959,46 +994,45 @@
       <c r="C4" t="n">
         <v>876</v>
       </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>1349824</v>
       </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.0906</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Negligenciável</t>
+          <t>Masc &gt; Fem</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Brasil — 2023</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1007,46 +1041,45 @@
       <c r="C5" t="n">
         <v>1099</v>
       </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>2236891</v>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.1317</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0.09760000000000001</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Negligenciável</t>
+          <t>Masc &gt; Fem</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Brasil — 2024</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1055,37 +1088,36 @@
       <c r="C6" t="n">
         <v>1133</v>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="F6" t="n">
         <v>2376175</v>
       </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.1454</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.1081</v>
-      </c>
-      <c r="L6" t="inlineStr">
+          <t>Masc &gt; Fem</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Pequeno</t>
         </is>
@@ -1103,37 +1135,36 @@
       <c r="C7" t="n">
         <v>177</v>
       </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>73175</v>
       </c>
+      <c r="G7" t="n">
+        <v>0.115124</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.057562</v>
+        <v>0.0752</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.0512</v>
-      </c>
-      <c r="L7" t="inlineStr">
+          <t>Masc &gt; Fem</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Negligenciável</t>
         </is>
@@ -1151,37 +1182,36 @@
       <c r="C8" t="n">
         <v>341</v>
       </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>R$4k-6k</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="F8" t="n">
         <v>242069</v>
       </c>
+      <c r="G8" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>2e-06</v>
+        <v>0.1609</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0.1162</v>
-      </c>
-      <c r="L8" t="inlineStr">
+          <t>Masc &gt; Fem</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Pequeno</t>
         </is>
@@ -1199,37 +1229,36 @@
       <c r="C9" t="n">
         <v>33</v>
       </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>R$4k-6k</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="F9" t="n">
         <v>3425</v>
       </c>
+      <c r="G9" t="n">
+        <v>0.05758</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.02879</v>
+        <v>0.2068</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1326</v>
-      </c>
-      <c r="L9" t="inlineStr">
+          <t>Masc &gt; Fem</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Pequeno</t>
         </is>
@@ -1247,41 +1276,38 @@
       <c r="C10" t="n">
         <v>2283</v>
       </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="F10" t="n">
         <v>9290493</v>
       </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.1169</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Masc &gt; Fem</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Grande</t>
+          <t>Pequeno</t>
         </is>
       </c>
     </row>
@@ -1297,276 +1323,38 @@
       <c r="C11" t="n">
         <v>629</v>
       </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>R$8k-12k</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>R$8k-12k</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>R$6k-8k</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>800021</v>
       </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.1631</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0.1191</v>
-      </c>
-      <c r="L11" t="inlineStr">
+          <t>Masc &gt; Fem</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Pequeno</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>β (log-odds/ano)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>IC 95% OR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p-valor</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Significativo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Tendência</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Brasil — Geral</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.0585</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1.0603</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[1.025, 1.097]</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.000711</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Crescente</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Região: Centro-Oeste</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.1202</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[0.971, 1.292]</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.119501</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Estável</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Região: Nordeste</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.0407</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.0415</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[0.940, 1.155]</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.439353</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Estável</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Região: Norte</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-0.0507</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9505</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[0.691, 1.308]</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.755645</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Estável</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Região: Sudeste</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.0557</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.0573</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[1.013, 1.103]</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.01041</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Crescente</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Região: Sul</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.0722</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.0748</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>[0.989, 1.169]</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.09075800000000001</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Estável</t>
         </is>
       </c>
     </row>

--- a/resultados_estatisticos.xlsx
+++ b/resultados_estatisticos.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chi2 e Cramer V" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mann-Whitney Salarial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spearman Nivel x Salario" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spearman Exp x Salario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tendencia Temporal" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1361,4 +1364,535 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ρ (Senioridade × Salário)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>p-valor</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Significativo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9342</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Forte</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2979</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7178</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Forte</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12321</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7221</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Forte</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ρ (Experiência × Salário)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>p-valor</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Significativo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10409</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6566</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Forte</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3108</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Forte</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>13517</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6522</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Forte</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>β (log-odds/ano)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>IC 95% OR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>p-valor</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Significativo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>McFadden R²</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tendência</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Brasil — Geral</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17295</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0603</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[1.025, 1.097]</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.000711</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Crescente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Região: Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1071</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.1202</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[0.971, 1.292]</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.119501</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Região: Nordeste</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1971</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0415</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[0.940, 1.155]</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.439353</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Região: Norte</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>256</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.0507</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[0.691, 1.308]</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.755645</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Região: Sudeste</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10542</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.0573</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[1.013, 1.103]</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Crescente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Região: Sul</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3044</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0748</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[0.989, 1.169]</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.09075800000000001</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/resultados_estatisticos.xlsx
+++ b/resultados_estatisticos.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chi2 e Cramer V" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mann-Whitney Salarial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spearman Nivel x Salario" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spearman Exp x Salario" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tendencia Temporal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H1-H2 Chi2 Cramer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H3 Mann-Whitney" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H4a Spearman Nivel" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H4b Spearman Exp" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H5 Tendencia Temporal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H6 IA Genero" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -831,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,6 +891,26 @@
           <t>Magnitude</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>% Masc &gt; Mediana</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>IC 95% Wilson Masc</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>% Fem &gt; Mediana</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>IC 95% Wilson Fem</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -937,6 +958,26 @@
           <t>Pequeno</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>33.7%</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[0.329, 0.346]</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>23.4%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>[0.220, 0.248]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -984,6 +1025,26 @@
           <t>Pequeno</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>46.6%</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[0.443, 0.488]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>38.1%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[0.337, 0.428]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1031,6 +1092,26 @@
           <t>Pequeno</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>50.1%</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[0.482, 0.520]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>[0.377, 0.442]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1078,6 +1159,26 @@
           <t>Pequeno</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>33.1%</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[0.316, 0.347]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[0.214, 0.264]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1125,6 +1226,26 @@
           <t>Pequeno</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[0.396, 0.428]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>28.4%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>[0.259, 0.311]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1172,6 +1293,26 @@
           <t>Negligenciável</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>31.1%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>[0.279, 0.344]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>30.5%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[0.242, 0.376]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1219,6 +1360,26 @@
           <t>Pequeno</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>42.6%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>[0.399, 0.454]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>27.9%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[0.234, 0.328]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1266,6 +1427,26 @@
           <t>Pequeno</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>[0.336, 0.482]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[0.067, 0.309]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1313,6 +1494,26 @@
           <t>Pequeno</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>36.2%</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>[0.351, 0.373]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>26.4%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[0.246, 0.282]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1358,6 +1559,26 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>51.2%</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[0.491, 0.533]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>[0.355, 0.431]</t>
         </is>
       </c>
     </row>
@@ -1895,4 +2116,1020 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>% Masculino</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>IC 95% Masc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>% Feminino</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>IC 95% Fem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Gap (M−F) pp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>χ²</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p-valor</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>V de Cramér</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Sig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Não usa IA</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[0.172, 0.201]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[0.203, 0.257]</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.982</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.004724</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Usa IA gratuita (ChatGPT free)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[0.612, 0.648]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[0.625, 0.686]</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.15053</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Usa IA paga (bolso próprio)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[0.073, 0.093]</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[0.020, 0.042]</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>30.806</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Usa IA paga (empresa paga)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[0.059, 0.078]</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[0.037, 0.064]</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.034932</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Usa Copilot / CodeWhisperer</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[0.113, 0.137]</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[0.078, 0.116]</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.936</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.014832</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IA é prioridade alta na empresa</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>37</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[0.336, 0.406]</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[0.263, 0.404]</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.322535</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Uso difuso/bottom-up na organização</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[0.436, 0.469]</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[0.360, 0.418]</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13.639</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Não usa IA</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[0.055, 0.073]</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[0.057, 0.091]</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.341325</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Usa IA gratuita (ChatGPT free)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[0.513, 0.550]</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[0.522, 0.587]</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.232918</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Usa IA paga (bolso próprio)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[0.155, 0.183]</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[0.097, 0.138]</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14.236</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.000161</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Usa IA paga (empresa paga)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[0.172, 0.202]</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[0.184, 0.237]</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.133855</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Usa Copilot / CodeWhisperer</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[0.229, 0.261]</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[0.187, 0.241]</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.741</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05308</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IA é prioridade alta na empresa</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[0.500, 0.567]</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[0.489, 0.626]</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5285530000000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Uso difuso/bottom-up na organização</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[0.476, 0.509]</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[0.407, 0.466]</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10.474</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.001211</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023–2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Não usa IA</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[0.118, 0.135]</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[0.136, 0.169]</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.854</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.005072</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023–2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Usa IA gratuita (ChatGPT free)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[0.569, 0.595]</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[0.584, 0.629]</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.328</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.068096</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2023–2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Usa IA paga (bolso próprio)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[0.116, 0.134]</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[0.061, 0.085]</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.07240000000000001</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2023–2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Usa IA paga (empresa paga)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[0.118, 0.135]</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[0.113, 0.144]</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.847787</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2023–2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Usa Copilot / CodeWhisperer</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[0.173, 0.194]</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[0.137, 0.170]</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.676</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.003224</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2023–2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IA é prioridade alta na empresa</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[0.433, 0.482]</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[0.403, 0.505]</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.879507</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2023–2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Uso difuso/bottom-up na organização</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[0.461, 0.484]</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[0.392, 0.433]</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23.872</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/resultados_estatisticos.xlsx
+++ b/resultados_estatisticos.xlsx
@@ -2237,7 +2237,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Usa IA gratuita (ChatGPT free)</t>
+          <t>Usa IA gratuita</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Usa Copilot / CodeWhisperer</t>
+          <t>Usa Copilot</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Usa IA gratuita (ChatGPT free)</t>
+          <t>Usa IA gratuita</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Usa Copilot / CodeWhisperer</t>
+          <t>Usa Copilot</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Usa IA gratuita (ChatGPT free)</t>
+          <t>Usa IA gratuita</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Usa Copilot / CodeWhisperer</t>
+          <t>Usa Copilot</t>
         </is>
       </c>
       <c r="C20" t="n">

--- a/resultados_estatisticos.xlsx
+++ b/resultados_estatisticos.xlsx
@@ -2462,7 +2462,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Uso difuso/bottom-up na organização</t>
+          <t>Uso difuso na organização</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Uso difuso/bottom-up na organização</t>
+          <t>Uso difuso na organização</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uso difuso/bottom-up na organização</t>
+          <t>Uso difuso na organização</t>
         </is>
       </c>
       <c r="C22" t="n">

--- a/resultados_estatisticos.xlsx
+++ b/resultados_estatisticos.xlsx
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10409</v>
+        <v>11900</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6566</v>
+        <v>0.6397</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3108</v>
+        <v>3538</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6296</v>
+        <v>0.6145</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13517</v>
+        <v>15438</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6522</v>
+        <v>0.636</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>0.004724</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0461</v>
+        <v>0.0423</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>0.15053</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0235</v>
+        <v>0.016</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0907</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>0.034932</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0345</v>
+        <v>0.0289</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>0.014832</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0398</v>
+        <v>0.0352</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>0.322535</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0331</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>0.000222</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0544</v>
+        <v>0.0519</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>0.341325</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>0.232918</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0199</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>0.000161</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0629</v>
+        <v>0.0597</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>0.133855</v>
       </c>
       <c r="J12" t="n">
-        <v>0.025</v>
+        <v>0.0175</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0.05308</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0322</v>
+        <v>0.0267</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>0.5285530000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0196</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>0.001211</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0478</v>
+        <v>0.0449</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>0.005072</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0327</v>
+        <v>0.03</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>0.068096</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0213</v>
+        <v>0.0174</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>0.847787</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0022</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>0.003224</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0344</v>
+        <v>0.0319</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>0.879507</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>1e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>0.051</v>
+        <v>0.0496</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>

--- a/resultados_estatisticos.xlsx
+++ b/resultados_estatisticos.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H1-H2 Chi2 Cramer" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H3 Mann-Whitney" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H4a Spearman Nivel" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H4b Spearman Exp" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H5 Tendencia Temporal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H6 IA Genero" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H3 Robustez Granularidade" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H4a Spearman Nivel" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H4b Spearman Exp" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H5 Tendencia Temporal" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H6 IA Genero" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1599,110 +1600,116 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Grupo</t>
+          <t>Granularidade</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Teste</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ρ (Senioridade × Salário)</t>
+          <t>Efeito</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Magnitude</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>p-valor</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Significativo</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Magnitude</t>
+          <t>Direção</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>9342</v>
+          <t>Ordinal completa (12 faixas)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mann-Whitney U</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="D2" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Forte</t>
+          <t>Masc &gt; Fem</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Feminino</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2979</v>
+          <t>3 classes (Baixa / Média / Alta)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mann-Whitney U</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7178</v>
-      </c>
-      <c r="D3" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Forte</t>
+          <t>Masc &gt; Fem</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>12321</v>
+          <t>Binária (Alta remuneração vs. demais)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Qui-Quadrado + V de Cramér</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7221</v>
-      </c>
-      <c r="D4" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Negligenciável</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Forte</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1740,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ρ (Experiência × Salário)</t>
+          <t>ρ (Senioridade × Salário)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1759,10 +1766,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11900</v>
+        <v>9342</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6397</v>
+        <v>0.722</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1785,10 +1792,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3538</v>
+        <v>2979</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6145</v>
+        <v>0.7178</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1811,10 +1818,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15438</v>
+        <v>12321</v>
       </c>
       <c r="C4" t="n">
-        <v>0.636</v>
+        <v>0.7221</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1841,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1857,259 +1864,100 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>β (log-odds/ano)</t>
+          <t>ρ (Experiência × Salário)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>p-valor</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>IC 95% OR</t>
+          <t>Significativo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>p-valor</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Significativo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>McFadden R²</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Tendência</t>
+          <t>Magnitude</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Brasil — Geral</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17295</v>
+        <v>11900</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0585</v>
+        <v>0.6397</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0603</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[1.025, 1.097]</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.000711</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Crescente</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Forte</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Região: Centro-Oeste</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1071</v>
+        <v>3538</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1135</v>
+        <v>0.6145</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1202</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[0.971, 1.292]</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.119501</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Estável</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Forte</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Região: Nordeste</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1971</v>
+        <v>15438</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0407</v>
+        <v>0.636</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0415</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[0.940, 1.155]</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.439353</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Estável</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Região: Norte</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>256</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.0507</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9505</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[0.691, 1.308]</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.755645</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Estável</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Região: Sudeste</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>10542</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0557</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.0573</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[1.013, 1.103]</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.01041</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Crescente</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Região: Sul</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3044</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0722</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.0748</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[0.989, 1.169]</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.09075800000000001</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Estável</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Forte</t>
         </is>
       </c>
     </row>
@@ -2124,6 +1972,289 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>β (log-odds/ano)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>IC 95% OR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>p-valor</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Significativo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>McFadden R²</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tendência</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Brasil — Geral</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17295</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0603</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[1.025, 1.097]</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.000711</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Crescente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Região: Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1071</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.1202</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[0.971, 1.292]</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.119501</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Região: Nordeste</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1971</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0415</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[0.940, 1.155]</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.439353</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Região: Norte</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>256</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.0507</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[0.691, 1.308]</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.755645</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Região: Sudeste</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10542</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.0573</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[1.013, 1.103]</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Crescente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Região: Sul</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3044</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0748</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[0.989, 1.169]</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.09075800000000001</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/resultados_estatisticos.xlsx
+++ b/resultados_estatisticos.xlsx
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12422</v>
+        <v>12412</v>
       </c>
       <c r="C2" t="n">
-        <v>47.763</v>
+        <v>47.675</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15438</v>
+        <v>15427</v>
       </c>
       <c r="C3" t="n">
-        <v>184.015</v>
+        <v>183.304</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.1059</v>
+        <v>0.1057</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17269</v>
+        <v>15779</v>
       </c>
       <c r="C4" t="n">
-        <v>89.471</v>
+        <v>81.755</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.0699</v>
+        <v>0.0697</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12422</v>
+        <v>12412</v>
       </c>
       <c r="C5" t="n">
-        <v>139.5</v>
+        <v>139.209</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.1037</v>
+        <v>0.1036</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15557</v>
+        <v>15546</v>
       </c>
       <c r="C6" t="n">
-        <v>60.57</v>
+        <v>60.654</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.0608</v>
+        <v>0.0609</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17295</v>
+        <v>15796</v>
       </c>
       <c r="C7" t="n">
-        <v>118.078</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.0794</v>
+        <v>0.0678</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16910</v>
+        <v>15484</v>
       </c>
       <c r="C8" t="n">
-        <v>539.484</v>
+        <v>484.014</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.1773</v>
+        <v>0.1753</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16884</v>
+        <v>15435</v>
       </c>
       <c r="C9" t="n">
-        <v>17.052</v>
+        <v>20.349</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001889</v>
+        <v>0.000426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.0278</v>
+        <v>0.0325</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11900</v>
+        <v>11890</v>
       </c>
       <c r="C2" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23712840</v>
+        <v>23681980</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1264</v>
+        <v>0.1262</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[0.329, 0.346]</t>
+          <t>[0.328, 0.345]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3662</v>
+        <v>3652</v>
       </c>
       <c r="C6" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2376175</v>
+        <v>2366543</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.1454</v>
+        <v>0.1449</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[0.396, 0.428]</t>
+          <t>[0.395, 0.427]</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C7" t="n">
         <v>177</v>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73175</v>
+        <v>73038</v>
       </c>
       <c r="G7" t="n">
-        <v>0.115124</v>
+        <v>0.118137</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.0752</v>
+        <v>0.0746</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[0.279, 0.344]</t>
+          <t>[0.278, 0.343]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C8" t="n">
         <v>341</v>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>242069</v>
+        <v>241758</v>
       </c>
       <c r="G8" t="n">
-        <v>4e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.1609</v>
+        <v>0.1603</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[0.399, 0.454]</t>
+          <t>[0.398, 0.453]</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C9" t="n">
         <v>33</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3425</v>
+        <v>3418</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05758</v>
+        <v>0.052562</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.2068</v>
+        <v>0.2112</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[0.336, 0.482]</t>
+          <t>[0.338, 0.484]</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7287</v>
+        <v>7281</v>
       </c>
       <c r="C10" t="n">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9290493</v>
+        <v>9277106</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.1169</v>
+        <v>0.1167</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1264</v>
+        <v>0.1262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1075</v>
+        <v>0.1073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9342</v>
+        <v>9333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.722</v>
+        <v>0.7218</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="C3" t="n">
         <v>0.7178</v>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12321</v>
+        <v>12311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7221</v>
+        <v>0.722</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11900</v>
+        <v>11890</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6397</v>
+        <v>0.6394</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6145</v>
+        <v>0.6146</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15438</v>
+        <v>15427</v>
       </c>
       <c r="C4" t="n">
-        <v>0.636</v>
+        <v>0.6358</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17295</v>
+        <v>15796</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0585</v>
+        <v>0.066</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0603</v>
+        <v>1.0683</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[1.025, 1.097]</t>
+          <t>[1.031, 1.107]</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.000711</v>
+        <v>0.000279</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2066,21 +2066,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1071</v>
+        <v>978</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1135</v>
+        <v>0.1263</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1202</v>
+        <v>1.1346</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[0.971, 1.292]</t>
+          <t>[0.975, 1.320]</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.119501</v>
+        <v>0.101903</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.0023</v>
+        <v>0.0029</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2103,21 +2103,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1971</v>
+        <v>1658</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0407</v>
+        <v>0.0377</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0415</v>
+        <v>1.0384</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[0.940, 1.155]</t>
+          <t>[0.927, 1.164]</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.439353</v>
+        <v>0.516809</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0507</v>
+        <v>-0.0452</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9505</v>
+        <v>0.9558</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[0.691, 1.308]</t>
+          <t>[0.660, 1.384]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.755645</v>
+        <v>0.8108610000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10542</v>
+        <v>9720</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0557</v>
+        <v>0.0623</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0573</v>
+        <v>1.0643</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[1.013, 1.103]</t>
+          <t>[1.018, 1.113]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.01041</v>
+        <v>0.006047</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3044</v>
+        <v>2866</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0722</v>
+        <v>0.0828</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0748</v>
+        <v>1.0863</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[0.989, 1.169]</t>
+          <t>[0.997, 1.184]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.09075800000000001</v>
+        <v>0.059978</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2271,45 +2271,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>População</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>% Masculino</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IC 95% Masc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>% Feminino</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>IC 95% Fem</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Gap (M−F) pp</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>χ²</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p-valor</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>V de Cramér</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sig.</t>
         </is>
@@ -2326,35 +2331,40 @@
           <t>Não usa IA</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>18.6</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>[0.172, 0.201]</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>22.9</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>[0.203, 0.257]</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>7.982</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.004724</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.0423</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>**</t>
         </is>
@@ -2371,35 +2381,40 @@
           <t>Usa IA gratuita</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>63</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>[0.612, 0.648]</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>65.7</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>[0.625, 0.686]</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2.067</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.15053</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.016</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -2416,35 +2431,40 @@
           <t>Usa IA paga (bolso próprio)</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>[0.073, 0.093]</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>2.9</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>[0.020, 0.042]</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>5.3</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>30.806</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.08790000000000001</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -2461,35 +2481,40 @@
           <t>Usa IA paga (empresa paga)</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>6.8</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>[0.059, 0.078]</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>4.9</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>[0.037, 0.064]</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1.9</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4.449</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.034932</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.0289</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -2506,35 +2531,40 @@
           <t>Usa Copilot</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>12.5</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>[0.113, 0.137]</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>9.5</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>[0.078, 0.116]</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>5.936</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.014832</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.0352</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>*</t>
         </is>
@@ -2551,35 +2581,40 @@
           <t>IA é prioridade alta na empresa</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>37</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>[0.336, 0.406]</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>32.9</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>[0.263, 0.404]</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4.1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.979</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.322535</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -2596,35 +2631,40 @@
           <t>Uso difuso na organização</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>45.3</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>[0.436, 0.469]</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>38.9</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>[0.360, 0.418]</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>6.4</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>13.639</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.000222</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.0519</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -2641,35 +2681,40 @@
           <t>Não usa IA</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>6.3</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>[0.055, 0.073]</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>7.2</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>[0.057, 0.091]</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.905</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.341325</v>
+        <v>0.959</v>
       </c>
       <c r="J9" t="n">
+        <v>0.327454</v>
+      </c>
+      <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -2686,35 +2731,40 @@
           <t>Usa IA gratuita</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>[0.513, 0.550]</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[0.512, 0.550]</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>55.5</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>[0.522, 0.587]</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-2.3</v>
-      </c>
       <c r="H10" t="n">
-        <v>1.423</v>
+        <v>-2.4</v>
       </c>
       <c r="I10" t="n">
-        <v>0.232918</v>
+        <v>1.534</v>
       </c>
       <c r="J10" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="K10" t="inlineStr">
+        <v>0.215524</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -2731,35 +2781,40 @@
           <t>Usa IA paga (bolso próprio)</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[0.155, 0.183]</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>11.6</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[0.097, 0.138]</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[0.097, 0.139]</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>5.3</v>
       </c>
-      <c r="H11" t="n">
-        <v>14.236</v>
-      </c>
       <c r="I11" t="n">
-        <v>0.000161</v>
+        <v>14.205</v>
       </c>
       <c r="J11" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.0597</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -2776,35 +2831,40 @@
           <t>Usa IA paga (empresa paga)</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>[0.172, 0.202]</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[0.184, 0.237]</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>-2.3</v>
+      <c r="F12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[0.183, 0.236]</t>
+        </is>
       </c>
       <c r="H12" t="n">
-        <v>2.247</v>
+        <v>-2.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.133855</v>
+        <v>2.112</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="K12" t="inlineStr">
+        <v>0.146143</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -2821,35 +2881,40 @@
           <t>Usa Copilot</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>[0.229, 0.261]</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>21.3</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>[0.187, 0.241]</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>3.2</v>
       </c>
-      <c r="H13" t="n">
-        <v>3.741</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.05308</v>
+        <v>3.76</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0267</v>
-      </c>
-      <c r="K13" t="inlineStr">
+        <v>0.052498</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -2866,35 +2931,40 @@
           <t>IA é prioridade alta na empresa</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>[0.500, 0.567]</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[0.500, 0.568]</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>55.8</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>[0.489, 0.626]</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-2.5</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.397</v>
+        <v>-2.4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5285530000000001</v>
+        <v>0.377</v>
       </c>
       <c r="J14" t="n">
+        <v>0.539207</v>
+      </c>
+      <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -2911,35 +2981,40 @@
           <t>Uso difuso na organização</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>49.2</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>[0.476, 0.509]</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[0.475, 0.508]</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>[0.407, 0.466]</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="H15" t="n">
-        <v>10.474</v>
+        <v>5.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001211</v>
+        <v>10.145</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0449</v>
-      </c>
-      <c r="K15" t="inlineStr">
+        <v>0.001447</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>**</t>
         </is>
@@ -2956,35 +3031,40 @@
           <t>Não usa IA</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>12.6</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>[0.118, 0.135]</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>15.2</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>[0.136, 0.169]</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H16" t="n">
-        <v>7.854</v>
-      </c>
       <c r="I16" t="n">
-        <v>0.005072</v>
+        <v>7.896</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K16" t="inlineStr">
+        <v>0.004954</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>**</t>
         </is>
@@ -3001,35 +3081,40 @@
           <t>Usa IA gratuita</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>58.2</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>[0.569, 0.595]</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>[0.584, 0.629]</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-2.4</v>
-      </c>
       <c r="H17" t="n">
-        <v>3.328</v>
+        <v>-2.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.068096</v>
+        <v>3.435</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0174</v>
-      </c>
-      <c r="K17" t="inlineStr">
+        <v>0.06382699999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -3046,35 +3131,40 @@
           <t>Usa IA paga (bolso próprio)</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>12.5</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>[0.116, 0.134]</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>7.2</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>[0.061, 0.085]</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>5.3</v>
       </c>
-      <c r="H18" t="n">
-        <v>38.52</v>
-      </c>
       <c r="I18" t="n">
+        <v>38.432</v>
+      </c>
+      <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -3091,35 +3181,40 @@
           <t>Usa IA paga (empresa paga)</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>12.6</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[0.118, 0.135]</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[0.113, 0.144]</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.2</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[0.117, 0.135]</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[0.113, 0.143]</t>
+        </is>
       </c>
       <c r="H19" t="n">
-        <v>0.037</v>
+        <v>-0.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.847787</v>
+        <v>0.025</v>
       </c>
       <c r="J19" t="n">
+        <v>0.873869</v>
+      </c>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -3136,35 +3231,40 @@
           <t>Usa Copilot</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Não-gestor</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>18.3</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>[0.173, 0.194]</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>15.3</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>[0.137, 0.170]</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="n">
-        <v>8.676</v>
-      </c>
       <c r="I20" t="n">
-        <v>0.003224</v>
+        <v>8.666</v>
       </c>
       <c r="J20" t="n">
+        <v>0.003241</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.0319</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>**</t>
         </is>
@@ -3181,35 +3281,40 @@
           <t>IA é prioridade alta na empresa</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>45.8</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>[0.433, 0.482]</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[0.433, 0.483]</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>45.3</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>[0.403, 0.505]</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0.4</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.023</v>
+        <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>0.879507</v>
+        <v>0.026</v>
       </c>
       <c r="J21" t="n">
+        <v>0.87154</v>
+      </c>
+      <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -3226,35 +3331,40 @@
           <t>Uso difuso na organização</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>47.2</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[0.461, 0.484]</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[0.460, 0.484]</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>41.3</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>[0.392, 0.433]</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>6</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[0.392, 0.434]</t>
+        </is>
       </c>
       <c r="H22" t="n">
-        <v>23.872</v>
+        <v>5.9</v>
       </c>
       <c r="I22" t="n">
+        <v>23.508</v>
+      </c>
+      <c r="J22" t="n">
         <v>1e-06</v>
       </c>
-      <c r="J22" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>***</t>
         </is>
